--- a/excel_bai_tap/bai5_bang_ke_hang_nhap.xlsx
+++ b/excel_bai_tap/bai5_bang_ke_hang_nhap.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t xml:space="preserve">BẢNG KÊ HÀNG NHẬP CỬA HÀNG SÁCH</t>
   </si>
@@ -71,27 +71,6 @@
   </si>
   <si>
     <t xml:space="preserve">TB trị giá | Cước VC thấp nhất | Thuế cao nhất | Cộng lớn nhất</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yêu cầu:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trị giá = số lượng * đơn giá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thuế= Trị giá *3,25%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cước VC= Số lượng *1,12%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cộng =Trị giá +Thuế +Cước VC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính tổng : Trị giá, Cước VC, thuế, Cộng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính thuế cao nhất, Cước VC thấp nhất, bình quân trị giá, Tổng cộng lớn nhất.</t>
   </si>
   <si>
     <t xml:space="preserve">Tham số (ô nhập, tô vàng):</t>
@@ -113,7 +92,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,14 +149,6 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="13"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="0"/>
@@ -252,7 +223,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -301,15 +272,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -565,7 +532,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -631,11 +598,11 @@
         <v>2070000</v>
       </c>
       <c r="F3" s="6" t="n">
-        <f aca="false">C3*$C$22</f>
+        <f aca="false">C3*$C$14</f>
         <v>0.5152</v>
       </c>
       <c r="G3" s="7" t="n">
-        <f aca="false">E3*$C$21</f>
+        <f aca="false">E3*$C$13</f>
         <v>67275</v>
       </c>
       <c r="H3" s="7" t="n">
@@ -661,11 +628,11 @@
         <v>1749600</v>
       </c>
       <c r="F4" s="6" t="n">
-        <f aca="false">C4*$C$22</f>
+        <f aca="false">C4*$C$14</f>
         <v>0.8064</v>
       </c>
       <c r="G4" s="7" t="n">
-        <f aca="false">E4*$C$21</f>
+        <f aca="false">E4*$C$13</f>
         <v>56862</v>
       </c>
       <c r="H4" s="7" t="n">
@@ -691,11 +658,11 @@
         <v>4617000</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">C5*$C$22</f>
+        <f aca="false">C5*$C$14</f>
         <v>0.9072</v>
       </c>
       <c r="G5" s="7" t="n">
-        <f aca="false">E5*$C$21</f>
+        <f aca="false">E5*$C$13</f>
         <v>150052.5</v>
       </c>
       <c r="H5" s="7" t="n">
@@ -721,11 +688,11 @@
         <v>3544800</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">C6*$C$22</f>
+        <f aca="false">C6*$C$14</f>
         <v>1.344</v>
       </c>
       <c r="G6" s="7" t="n">
-        <f aca="false">E6*$C$21</f>
+        <f aca="false">E6*$C$13</f>
         <v>115206</v>
       </c>
       <c r="H6" s="7" t="n">
@@ -751,11 +718,11 @@
         <v>1629000</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">C7*$C$22</f>
+        <f aca="false">C7*$C$14</f>
         <v>0.336</v>
       </c>
       <c r="G7" s="7" t="n">
-        <f aca="false">E7*$C$21</f>
+        <f aca="false">E7*$C$13</f>
         <v>52942.5</v>
       </c>
       <c r="H7" s="7" t="n">
@@ -781,11 +748,11 @@
         <v>1351600</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">C8*$C$22</f>
+        <f aca="false">C8*$C$14</f>
         <v>1.2208</v>
       </c>
       <c r="G8" s="7" t="n">
-        <f aca="false">E8*$C$21</f>
+        <f aca="false">E8*$C$13</f>
         <v>43927</v>
       </c>
       <c r="H8" s="7" t="n">
@@ -835,59 +802,24 @@
         <v>4767053.4072</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>18</v>
       </c>
+      <c r="C13" s="13" t="n">
+        <v>0.0325</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
+      <c r="B14" s="12" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>0.0325</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="14" t="n">
+      <c r="C14" s="13" t="n">
         <v>0.0112</v>
       </c>
     </row>

--- a/excel_bai_tap/bai5_bang_ke_hang_nhap.xlsx
+++ b/excel_bai_tap/bai5_bang_ke_hang_nhap.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t xml:space="preserve">BẢNG KÊ HÀNG NHẬP CỬA HÀNG SÁCH</t>
   </si>
@@ -68,31 +68,18 @@
   </si>
   <si>
     <t xml:space="preserve">Tổng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB trị giá | Cước VC thấp nhất | Thuế cao nhất | Cộng lớn nhất</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tham số (ô nhập, tô vàng):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thuế suất (trên trị giá)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cước VC (trên số lượng)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,23 +133,8 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0000FF"/>
-      <name val="Times New Roman"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -173,12 +145,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC5D9F1"/>
         <bgColor rgb="FFC0C0C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -223,7 +189,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -265,18 +231,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -532,7 +486,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -598,11 +552,11 @@
         <v>2070000</v>
       </c>
       <c r="F3" s="6" t="n">
-        <f aca="false">C3*$C$14</f>
+        <f aca="false">C3*0.0112</f>
         <v>0.5152</v>
       </c>
       <c r="G3" s="7" t="n">
-        <f aca="false">E3*$C$13</f>
+        <f aca="false">E3*0.0325</f>
         <v>67275</v>
       </c>
       <c r="H3" s="7" t="n">
@@ -628,11 +582,11 @@
         <v>1749600</v>
       </c>
       <c r="F4" s="6" t="n">
-        <f aca="false">C4*$C$14</f>
+        <f aca="false">C4*0.0112</f>
         <v>0.8064</v>
       </c>
       <c r="G4" s="7" t="n">
-        <f aca="false">E4*$C$13</f>
+        <f aca="false">E4*0.0325</f>
         <v>56862</v>
       </c>
       <c r="H4" s="7" t="n">
@@ -658,11 +612,11 @@
         <v>4617000</v>
       </c>
       <c r="F5" s="6" t="n">
-        <f aca="false">C5*$C$14</f>
+        <f aca="false">C5*0.0112</f>
         <v>0.9072</v>
       </c>
       <c r="G5" s="7" t="n">
-        <f aca="false">E5*$C$13</f>
+        <f aca="false">E5*0.0325</f>
         <v>150052.5</v>
       </c>
       <c r="H5" s="7" t="n">
@@ -688,11 +642,11 @@
         <v>3544800</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">C6*$C$14</f>
+        <f aca="false">C6*0.0112</f>
         <v>1.344</v>
       </c>
       <c r="G6" s="7" t="n">
-        <f aca="false">E6*$C$13</f>
+        <f aca="false">E6*0.0325</f>
         <v>115206</v>
       </c>
       <c r="H6" s="7" t="n">
@@ -718,11 +672,11 @@
         <v>1629000</v>
       </c>
       <c r="F7" s="6" t="n">
-        <f aca="false">C7*$C$14</f>
+        <f aca="false">C7*0.0112</f>
         <v>0.336</v>
       </c>
       <c r="G7" s="7" t="n">
-        <f aca="false">E7*$C$13</f>
+        <f aca="false">E7*0.0325</f>
         <v>52942.5</v>
       </c>
       <c r="H7" s="7" t="n">
@@ -748,11 +702,11 @@
         <v>1351600</v>
       </c>
       <c r="F8" s="6" t="n">
-        <f aca="false">C8*$C$14</f>
+        <f aca="false">C8*0.0112</f>
         <v>1.2208</v>
       </c>
       <c r="G8" s="7" t="n">
-        <f aca="false">E8*$C$13</f>
+        <f aca="false">E8*0.0325</f>
         <v>43927</v>
       </c>
       <c r="H8" s="7" t="n">
@@ -782,9 +736,6 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="s">
-        <v>16</v>
-      </c>
       <c r="E10" s="9" t="n">
         <f aca="false">AVERAGE(E3:E8)</f>
         <v>2493666.66666667</v>
@@ -800,27 +751,6 @@
       <c r="H10" s="10" t="n">
         <f aca="false">MAX(H3:H8)</f>
         <v>4767053.4072</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>0.0325</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>0.0112</v>
       </c>
     </row>
   </sheetData>
